--- a/data-sources/宝石表/技能养成相关.xlsx
+++ b/data-sources/宝石表/技能养成相关.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zaomeng\1.表格目录\XLS表格\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="11655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SkillActive" sheetId="1" r:id="rId1"/>
@@ -900,7 +905,7 @@
     <t>辅助有投射物标签的技能，使其生成的投射物数量+1，造成的伤害额外降低30%</t>
   </si>
   <si>
-    <t>10038|10046</t>
+    <t>10038|10146</t>
   </si>
   <si>
     <t>[[1],[-0.3]]</t>
@@ -1149,7 +1154,7 @@
     <t>辅助有环绕标签的技能，环绕子弹数量+1，造成的伤害额外降低30%</t>
   </si>
   <si>
-    <t>10131|10046</t>
+    <t>10131|10146</t>
   </si>
   <si>
     <t>包围·二</t>
